--- a/006_water_demand/水消費量記入シート.xlsx
+++ b/006_water_demand/水消費量記入シート.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\azure_ai\education\006_water_demand\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kinoshita.ryousuke\Desktop\develop\myself\ai_study\006_water_demand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D5F0D4-56DF-4F84-9880-DE446A25CDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2809FFE-5EEA-44CE-A85A-EFE3EDE7927E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="3" r:id="rId1"/>
@@ -32,9 +32,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -197,7 +198,7 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
@@ -246,16 +247,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -546,52 +546,52 @@
     <col min="3" max="15" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="24">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:15" ht="30" customHeight="1">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:15" ht="37.5" customHeight="1">
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="2:15" ht="45" customHeight="1">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="1"/>
@@ -608,7 +608,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="2:15" ht="45" customHeight="1">
+    <row r="4" spans="2:15" ht="54.75" customHeight="1">
       <c r="B4" s="5"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -624,8 +624,8 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="2:15" ht="45" customHeight="1">
-      <c r="B5" s="6" t="str">
+    <row r="5" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B5" s="3" t="str">
         <f>IF($B$4=0, "", B4+1)</f>
         <v/>
       </c>
@@ -642,8 +642,8 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="2:15" ht="45" customHeight="1">
-      <c r="B6" s="6" t="str">
+    <row r="6" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B6" s="3" t="str">
         <f t="shared" ref="B6:B34" si="0">IF($B$4=0, "", B5+1)</f>
         <v/>
       </c>
@@ -661,8 +661,8 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="2:15" ht="45" customHeight="1">
-      <c r="B7" s="6" t="str">
+    <row r="7" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B7" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -680,8 +680,8 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="2:15" ht="45" customHeight="1">
-      <c r="B8" s="6" t="str">
+    <row r="8" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B8" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -699,8 +699,8 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="2:15" ht="45" customHeight="1">
-      <c r="B9" s="6" t="str">
+    <row r="9" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B9" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -718,8 +718,8 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="2:15" ht="45" customHeight="1">
-      <c r="B10" s="6" t="str">
+    <row r="10" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B10" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -737,8 +737,8 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="2:15" ht="45" customHeight="1">
-      <c r="B11" s="6" t="str">
+    <row r="11" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B11" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -756,8 +756,8 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="2:15" ht="45" customHeight="1">
-      <c r="B12" s="6" t="str">
+    <row r="12" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B12" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -775,8 +775,8 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="2:15" ht="45" customHeight="1">
-      <c r="B13" s="6" t="str">
+    <row r="13" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B13" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -794,8 +794,8 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="2:15" ht="45" customHeight="1">
-      <c r="B14" s="6" t="str">
+    <row r="14" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B14" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -813,8 +813,8 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="2:15" ht="45" customHeight="1">
-      <c r="B15" s="6" t="str">
+    <row r="15" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B15" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -832,8 +832,8 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="2:15" ht="45" customHeight="1">
-      <c r="B16" s="6" t="str">
+    <row r="16" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B16" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -851,8 +851,8 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="2:15" ht="45" customHeight="1">
-      <c r="B17" s="6" t="str">
+    <row r="17" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B17" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -870,8 +870,8 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="2:15" ht="45" customHeight="1">
-      <c r="B18" s="6" t="str">
+    <row r="18" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B18" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -889,8 +889,8 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="2:15" ht="45" customHeight="1">
-      <c r="B19" s="6" t="str">
+    <row r="19" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B19" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -908,8 +908,8 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="2:15" ht="45" customHeight="1">
-      <c r="B20" s="6" t="str">
+    <row r="20" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B20" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -927,8 +927,8 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="2:15" ht="45" customHeight="1">
-      <c r="B21" s="6" t="str">
+    <row r="21" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B21" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -946,8 +946,8 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="2:15" ht="45" customHeight="1">
-      <c r="B22" s="6" t="str">
+    <row r="22" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B22" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -965,8 +965,8 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="2:15" ht="45" customHeight="1">
-      <c r="B23" s="6" t="str">
+    <row r="23" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B23" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -984,8 +984,8 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="2:15" ht="45" customHeight="1">
-      <c r="B24" s="6" t="str">
+    <row r="24" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B24" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1003,8 +1003,8 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="2:15" ht="45" customHeight="1">
-      <c r="B25" s="6" t="str">
+    <row r="25" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B25" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1022,8 +1022,8 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="2:15" ht="45" customHeight="1">
-      <c r="B26" s="6" t="str">
+    <row r="26" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B26" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1041,8 +1041,8 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="2:15" ht="45" customHeight="1">
-      <c r="B27" s="6" t="str">
+    <row r="27" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B27" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1060,8 +1060,8 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="2:15" ht="45" customHeight="1">
-      <c r="B28" s="6" t="str">
+    <row r="28" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B28" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1079,8 +1079,8 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="2:15" ht="45" customHeight="1">
-      <c r="B29" s="6" t="str">
+    <row r="29" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B29" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1098,8 +1098,8 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="2:15" ht="45" customHeight="1">
-      <c r="B30" s="6" t="str">
+    <row r="30" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B30" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1117,8 +1117,8 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="2:15" ht="45" customHeight="1">
-      <c r="B31" s="6" t="str">
+    <row r="31" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B31" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1136,8 +1136,8 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="2:15" ht="45" customHeight="1">
-      <c r="B32" s="6" t="str">
+    <row r="32" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B32" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1155,8 +1155,8 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="2:15" ht="45" customHeight="1">
-      <c r="B33" s="6" t="str">
+    <row r="33" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B33" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1174,8 +1174,8 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="2:15" ht="45" customHeight="1">
-      <c r="B34" s="6" t="str">
+    <row r="34" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B34" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -1196,7 +1196,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="42" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="41" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1213,52 +1213,52 @@
     <col min="3" max="15" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="24">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:15" ht="30">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:15" ht="37.5" customHeight="1">
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="2:15" ht="45" customHeight="1">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="1"/>
@@ -1275,8 +1275,8 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="2:15" ht="45" customHeight="1">
-      <c r="B4" s="4">
+    <row r="4" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B4" s="3">
         <v>46204</v>
       </c>
       <c r="C4" s="1"/>
@@ -1293,8 +1293,8 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="2:15" ht="45" customHeight="1">
-      <c r="B5" s="4">
+    <row r="5" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B5" s="3">
         <f>B4+1</f>
         <v>46205</v>
       </c>
@@ -1311,8 +1311,8 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="2:15" ht="45" customHeight="1">
-      <c r="B6" s="4">
+    <row r="6" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B6" s="3">
         <f>B5+1</f>
         <v>46206</v>
       </c>
@@ -1330,8 +1330,8 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="2:15" ht="45" customHeight="1">
-      <c r="B7" s="4">
+    <row r="7" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B7" s="3">
         <f t="shared" ref="B7:B34" si="0">B6+1</f>
         <v>46207</v>
       </c>
@@ -1349,8 +1349,8 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="2:15" ht="45" customHeight="1">
-      <c r="B8" s="4">
+    <row r="8" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B8" s="3">
         <f t="shared" si="0"/>
         <v>46208</v>
       </c>
@@ -1368,8 +1368,8 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="2:15" ht="45" customHeight="1">
-      <c r="B9" s="4">
+    <row r="9" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B9" s="3">
         <f t="shared" si="0"/>
         <v>46209</v>
       </c>
@@ -1387,8 +1387,8 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="2:15" ht="45" customHeight="1">
-      <c r="B10" s="4">
+    <row r="10" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B10" s="3">
         <f t="shared" si="0"/>
         <v>46210</v>
       </c>
@@ -1406,8 +1406,8 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="2:15" ht="45" customHeight="1">
-      <c r="B11" s="4">
+    <row r="11" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B11" s="3">
         <f t="shared" si="0"/>
         <v>46211</v>
       </c>
@@ -1425,8 +1425,8 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="2:15" ht="45" customHeight="1">
-      <c r="B12" s="4">
+    <row r="12" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B12" s="3">
         <f t="shared" si="0"/>
         <v>46212</v>
       </c>
@@ -1444,8 +1444,8 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="2:15" ht="45" customHeight="1">
-      <c r="B13" s="4">
+    <row r="13" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>46213</v>
       </c>
@@ -1463,8 +1463,8 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="2:15" ht="45" customHeight="1">
-      <c r="B14" s="4">
+    <row r="14" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>46214</v>
       </c>
@@ -1482,8 +1482,8 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="2:15" ht="45" customHeight="1">
-      <c r="B15" s="4">
+    <row r="15" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>46215</v>
       </c>
@@ -1501,8 +1501,8 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="2:15" ht="45" customHeight="1">
-      <c r="B16" s="4">
+    <row r="16" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>46216</v>
       </c>
@@ -1520,8 +1520,8 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="2:15" ht="45" customHeight="1">
-      <c r="B17" s="4">
+    <row r="17" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
@@ -1539,8 +1539,8 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="2:15" ht="45" customHeight="1">
-      <c r="B18" s="4">
+    <row r="18" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>46218</v>
       </c>
@@ -1558,8 +1558,8 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="2:15" ht="45" customHeight="1">
-      <c r="B19" s="4">
+    <row r="19" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>46219</v>
       </c>
@@ -1577,8 +1577,8 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="2:15" ht="45" customHeight="1">
-      <c r="B20" s="4">
+    <row r="20" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>46220</v>
       </c>
@@ -1596,8 +1596,8 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="2:15" ht="45" customHeight="1">
-      <c r="B21" s="4">
+    <row r="21" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>46221</v>
       </c>
@@ -1615,8 +1615,8 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="2:15" ht="45" customHeight="1">
-      <c r="B22" s="4">
+    <row r="22" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>46222</v>
       </c>
@@ -1634,8 +1634,8 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="2:15" ht="45" customHeight="1">
-      <c r="B23" s="4">
+    <row r="23" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>46223</v>
       </c>
@@ -1653,8 +1653,8 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="2:15" ht="45" customHeight="1">
-      <c r="B24" s="4">
+    <row r="24" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>46224</v>
       </c>
@@ -1672,8 +1672,8 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="2:15" ht="45" customHeight="1">
-      <c r="B25" s="4">
+    <row r="25" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>46225</v>
       </c>
@@ -1691,8 +1691,8 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="2:15" ht="45" customHeight="1">
-      <c r="B26" s="4">
+    <row r="26" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>46226</v>
       </c>
@@ -1710,8 +1710,8 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="2:15" ht="45" customHeight="1">
-      <c r="B27" s="4">
+    <row r="27" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>46227</v>
       </c>
@@ -1729,8 +1729,8 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="2:15" ht="45" customHeight="1">
-      <c r="B28" s="4">
+    <row r="28" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>46228</v>
       </c>
@@ -1748,8 +1748,8 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="2:15" ht="45" customHeight="1">
-      <c r="B29" s="4">
+    <row r="29" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>46229</v>
       </c>
@@ -1767,8 +1767,8 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="2:15" ht="45" customHeight="1">
-      <c r="B30" s="4">
+    <row r="30" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>46230</v>
       </c>
@@ -1786,8 +1786,8 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="2:15" ht="45" customHeight="1">
-      <c r="B31" s="4">
+    <row r="31" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B31" s="3">
         <f t="shared" si="0"/>
         <v>46231</v>
       </c>
@@ -1805,8 +1805,8 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="2:15" ht="45" customHeight="1">
-      <c r="B32" s="4">
+    <row r="32" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B32" s="3">
         <f t="shared" si="0"/>
         <v>46232</v>
       </c>
@@ -1824,8 +1824,8 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="2:15" ht="45" customHeight="1">
-      <c r="B33" s="4">
+    <row r="33" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B33" s="3">
         <f t="shared" si="0"/>
         <v>46233</v>
       </c>
@@ -1843,8 +1843,8 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="2:15" ht="45" customHeight="1">
-      <c r="B34" s="4">
+    <row r="34" spans="2:15" ht="54.75" customHeight="1">
+      <c r="B34" s="3">
         <f t="shared" si="0"/>
         <v>46234</v>
       </c>
@@ -1865,6 +1865,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="42" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="41" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/006_water_demand/水消費量記入シート.xlsx
+++ b/006_water_demand/水消費量記入シート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kinoshita.ryousuke\Desktop\develop\myself\ai_study\006_water_demand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2809FFE-5EEA-44CE-A85A-EFE3EDE7927E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE63C75-3EBD-422D-84FD-02B42D15DFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="202607" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'202607'!$A$1:$P$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'202607'!$A$1:$N$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">template!$A$1:$P$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t>氏名</t>
     <rPh sb="0" eb="2">
@@ -156,6 +156,37 @@
       <t>カイ</t>
     </rPh>
     <rPh sb="6" eb="7">
+      <t>リョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>岡村</t>
+    <rPh sb="0" eb="2">
+      <t>オカムラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>加藤</t>
+    <rPh sb="0" eb="2">
+      <t>カトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中川</t>
+    <rPh sb="0" eb="2">
+      <t>ナカガワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1回の量(L)</t>
+    <rPh sb="1" eb="2">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
       <t>リョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1206,14 +1237,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:O34"/>
+  <dimension ref="B2:M34"/>
   <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="21.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="15" width="14.375" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="13" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="30">
+    <row r="2" spans="2:13" ht="30">
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1242,24 +1273,18 @@
         <v>8</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" ht="45" customHeight="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" ht="45" customHeight="1">
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1272,10 +1297,8 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="4" spans="2:13" ht="51.75" customHeight="1">
       <c r="B4" s="3">
         <v>46204</v>
       </c>
@@ -1290,10 +1313,8 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="5" spans="2:13" ht="51.75" customHeight="1">
       <c r="B5" s="3">
         <f>B4+1</f>
         <v>46205</v>
@@ -1308,10 +1329,8 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="6" spans="2:13" ht="51.75" customHeight="1">
       <c r="B6" s="3">
         <f>B5+1</f>
         <v>46206</v>
@@ -1327,10 +1346,8 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="7" spans="2:13" ht="51.75" hidden="1" customHeight="1">
       <c r="B7" s="3">
         <f t="shared" ref="B7:B34" si="0">B6+1</f>
         <v>46207</v>
@@ -1346,10 +1363,8 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="8" spans="2:13" ht="51.75" hidden="1" customHeight="1">
       <c r="B8" s="3">
         <f t="shared" si="0"/>
         <v>46208</v>
@@ -1365,10 +1380,8 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="9" spans="2:13" ht="51.75" customHeight="1">
       <c r="B9" s="3">
         <f t="shared" si="0"/>
         <v>46209</v>
@@ -1384,10 +1397,8 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="10" spans="2:13" ht="51.75" customHeight="1">
       <c r="B10" s="3">
         <f t="shared" si="0"/>
         <v>46210</v>
@@ -1403,10 +1414,8 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="11" spans="2:13" ht="51.75" customHeight="1">
       <c r="B11" s="3">
         <f t="shared" si="0"/>
         <v>46211</v>
@@ -1422,10 +1431,8 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="12" spans="2:13" ht="51.75" customHeight="1">
       <c r="B12" s="3">
         <f t="shared" si="0"/>
         <v>46212</v>
@@ -1441,10 +1448,8 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="13" spans="2:13" ht="51.75" customHeight="1">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>46213</v>
@@ -1460,10 +1465,8 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="14" spans="2:13" ht="51.75" hidden="1" customHeight="1">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>46214</v>
@@ -1479,10 +1482,8 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="15" spans="2:13" ht="51.75" hidden="1" customHeight="1">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>46215</v>
@@ -1498,10 +1499,8 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="16" spans="2:13" ht="51.75" customHeight="1">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>46216</v>
@@ -1517,10 +1516,8 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="17" spans="2:13" ht="51.75" customHeight="1">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>46217</v>
@@ -1536,10 +1533,8 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="18" spans="2:13" ht="51.75" customHeight="1">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>46218</v>
@@ -1555,10 +1550,8 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="19" spans="2:13" ht="51.75" customHeight="1">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>46219</v>
@@ -1574,10 +1567,8 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="20" spans="2:13" ht="51.75" customHeight="1">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>46220</v>
@@ -1593,10 +1584,8 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="21" spans="2:13" ht="51.75" hidden="1" customHeight="1">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>46221</v>
@@ -1612,10 +1601,8 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="22" spans="2:13" ht="51.75" hidden="1" customHeight="1">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>46222</v>
@@ -1631,10 +1618,8 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="23" spans="2:13" ht="51.75" customHeight="1">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>46223</v>
@@ -1650,10 +1635,8 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="24" spans="2:13" ht="51.75" customHeight="1">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>46224</v>
@@ -1669,10 +1652,8 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="25" spans="2:13" ht="51.75" customHeight="1">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>46225</v>
@@ -1688,10 +1669,8 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="26" spans="2:13" ht="51.75" customHeight="1">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>46226</v>
@@ -1707,10 +1686,8 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="27" spans="2:13" ht="51.75" customHeight="1">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>46227</v>
@@ -1726,10 +1703,8 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="28" spans="2:13" ht="51.75" hidden="1" customHeight="1">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>46228</v>
@@ -1745,10 +1720,8 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="29" spans="2:13" ht="51.75" hidden="1" customHeight="1">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>46229</v>
@@ -1764,10 +1737,8 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="30" spans="2:13" ht="51.75" customHeight="1">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>46230</v>
@@ -1783,10 +1754,8 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="31" spans="2:13" ht="51.75" customHeight="1">
       <c r="B31" s="3">
         <f t="shared" si="0"/>
         <v>46231</v>
@@ -1802,10 +1771,8 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="32" spans="2:13" ht="51.75" customHeight="1">
       <c r="B32" s="3">
         <f t="shared" si="0"/>
         <v>46232</v>
@@ -1821,10 +1788,8 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-    </row>
-    <row r="33" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="33" spans="2:13" ht="51.75" customHeight="1">
       <c r="B33" s="3">
         <f t="shared" si="0"/>
         <v>46233</v>
@@ -1840,10 +1805,8 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" ht="54.75" customHeight="1">
+    </row>
+    <row r="34" spans="2:13" ht="51.75" customHeight="1">
       <c r="B34" s="3">
         <f t="shared" si="0"/>
         <v>46234</v>
@@ -1859,12 +1822,10 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="41" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="48" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>